--- a/SAW-analytics/src/dados/resultado/ranking_saw_pcj_2024.xlsx
+++ b/SAW-analytics/src/dados/resultado/ranking_saw_pcj_2024.xlsx
@@ -8,11 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ranking_geral" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Autarquia" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Empresa privada" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Município" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sociedade de economia mista" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indicadores" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_10" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bottom_10" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Autarquia" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Empresa privada" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Município" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sociedade de economia mista" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indicadores" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3220,7 +3222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3281,34 +3283,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rio das Pedras</t>
+          <t>Águas de São Pedro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Autarquia</t>
+          <t>Sociedade de economia mista</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5654832830138814</v>
+        <v>0.5680751715371495</v>
       </c>
       <c r="E2" t="n">
-        <v>96.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>26.84</v>
+        <v>18.09</v>
       </c>
       <c r="G2" t="n">
-        <v>56.97</v>
+        <v>4.9</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6</v>
+        <v>9.35</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>151.49</v>
+        <v>94.06</v>
       </c>
     </row>
     <row r="3">
@@ -3317,7 +3319,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Santa Bárbara D Oeste</t>
+          <t>Rio das Pedras</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3326,25 +3328,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5347131860269471</v>
+        <v>0.5654832830138814</v>
       </c>
       <c r="E3" t="n">
-        <v>99.43000000000001</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>22.78</v>
+        <v>26.84</v>
       </c>
       <c r="G3" t="n">
-        <v>47.21</v>
+        <v>56.97</v>
       </c>
       <c r="H3" t="n">
-        <v>2.42</v>
+        <v>0.6</v>
       </c>
       <c r="I3" t="n">
-        <v>99.05</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
-        <v>117.02</v>
+        <v>151.49</v>
       </c>
     </row>
     <row r="4">
@@ -3353,34 +3355,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Piracicaba</t>
+          <t>Cosmópolis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Autarquia</t>
+          <t>Município</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5325648407132801</v>
+        <v>0.5457524239468542</v>
       </c>
       <c r="E4" t="n">
-        <v>92.23</v>
+        <v>97.47</v>
       </c>
       <c r="F4" t="n">
-        <v>27.09</v>
+        <v>32.79</v>
       </c>
       <c r="G4" t="n">
-        <v>50.91</v>
+        <v>25.02</v>
       </c>
       <c r="H4" t="n">
-        <v>8.52</v>
+        <v>8.35</v>
       </c>
       <c r="I4" t="n">
-        <v>99.69</v>
+        <v>97.47</v>
       </c>
       <c r="J4" t="n">
-        <v>119.55</v>
+        <v>114.51</v>
       </c>
     </row>
     <row r="5">
@@ -3389,7 +3391,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dois Córregos</t>
+          <t>Santa Bárbara D Oeste</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3398,25 +3400,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5300423012009458</v>
+        <v>0.5347131860269471</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>20.46</v>
+        <v>22.78</v>
       </c>
       <c r="G5" t="n">
-        <v>42.4</v>
+        <v>47.21</v>
       </c>
       <c r="H5" t="n">
-        <v>0.91</v>
+        <v>2.42</v>
       </c>
       <c r="I5" t="n">
-        <v>96</v>
+        <v>99.05</v>
       </c>
       <c r="J5" t="n">
-        <v>121.93</v>
+        <v>117.02</v>
       </c>
     </row>
     <row r="6">
@@ -3425,7 +3427,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cordeirópolis</t>
+          <t>Piracicaba</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3434,25 +3436,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5260104700145199</v>
+        <v>0.5325648407132801</v>
       </c>
       <c r="E6" t="n">
-        <v>99</v>
+        <v>92.23</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>27.09</v>
       </c>
       <c r="G6" t="n">
-        <v>44.49</v>
+        <v>50.91</v>
       </c>
       <c r="H6" t="n">
-        <v>1.19</v>
+        <v>8.52</v>
       </c>
       <c r="I6" t="n">
-        <v>97.36</v>
+        <v>99.69</v>
       </c>
       <c r="J6" t="n">
-        <v>114.09</v>
+        <v>119.55</v>
       </c>
     </row>
     <row r="7">
@@ -3461,7 +3463,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Americana</t>
+          <t>Dois Córregos</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3470,25 +3472,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5219467392588566</v>
+        <v>0.5300423012009458</v>
       </c>
       <c r="E7" t="n">
-        <v>99.83</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>31.67</v>
+        <v>20.46</v>
       </c>
       <c r="G7" t="n">
-        <v>58.79</v>
+        <v>42.4</v>
       </c>
       <c r="H7" t="n">
-        <v>45.35</v>
+        <v>0.91</v>
       </c>
       <c r="I7" t="n">
-        <v>96.84</v>
+        <v>96</v>
       </c>
       <c r="J7" t="n">
-        <v>92.01000000000001</v>
+        <v>121.93</v>
       </c>
     </row>
     <row r="8">
@@ -3497,7 +3499,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pedreira</t>
+          <t>Cordeirópolis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3506,25 +3508,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5172977231558979</v>
+        <v>0.5260104700145199</v>
       </c>
       <c r="E8" t="n">
-        <v>98.33</v>
+        <v>99</v>
       </c>
       <c r="F8" t="n">
-        <v>29.38</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>58.36</v>
+        <v>44.49</v>
       </c>
       <c r="H8" t="n">
-        <v>52.05</v>
+        <v>1.19</v>
       </c>
       <c r="I8" t="n">
-        <v>97.34999999999999</v>
+        <v>97.36</v>
       </c>
       <c r="J8" t="n">
-        <v>91.66</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="9">
@@ -3533,7 +3535,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Engenheiro Coelho</t>
+          <t>Americana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3542,25 +3544,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.5165540506893349</v>
+        <v>0.5219467392588566</v>
       </c>
       <c r="E9" t="n">
-        <v>94.06999999999999</v>
+        <v>99.83</v>
       </c>
       <c r="F9" t="n">
-        <v>19.12</v>
+        <v>31.67</v>
       </c>
       <c r="G9" t="n">
-        <v>44.16</v>
+        <v>58.79</v>
       </c>
       <c r="H9" t="n">
-        <v>1.33</v>
+        <v>45.35</v>
       </c>
       <c r="I9" t="n">
-        <v>94.06999999999999</v>
+        <v>96.84</v>
       </c>
       <c r="J9" t="n">
-        <v>126.43</v>
+        <v>92.01000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -3569,34 +3571,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capivari</t>
+          <t>Rafard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Autarquia</t>
+          <t>Município</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.5081899659912953</v>
+        <v>0.5192770534226446</v>
       </c>
       <c r="E10" t="n">
-        <v>96.25</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>26.13</v>
+        <v>22.44</v>
       </c>
       <c r="G10" t="n">
-        <v>38.16</v>
+        <v>32.96</v>
       </c>
       <c r="H10" t="n">
-        <v>6.11</v>
+        <v>0.06</v>
       </c>
       <c r="I10" t="n">
-        <v>96.25</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -3605,7 +3607,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indaiatuba</t>
+          <t>Pedreira</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3614,349 +3616,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5072676042789033</v>
+        <v>0.5172977231558979</v>
       </c>
       <c r="E11" t="n">
-        <v>95.09</v>
+        <v>98.33</v>
       </c>
       <c r="F11" t="n">
-        <v>23.31</v>
+        <v>29.38</v>
       </c>
       <c r="G11" t="n">
-        <v>38.95</v>
+        <v>58.36</v>
       </c>
       <c r="H11" t="n">
-        <v>6.29</v>
+        <v>52.05</v>
       </c>
       <c r="I11" t="n">
-        <v>94.41</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>102.99</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Brotas</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Autarquia</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.4964879726116124</v>
-      </c>
-      <c r="E12" t="n">
-        <v>92.12</v>
-      </c>
-      <c r="F12" t="n">
-        <v>22.02</v>
-      </c>
-      <c r="G12" t="n">
-        <v>29.39</v>
-      </c>
-      <c r="H12" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>90.06999999999999</v>
-      </c>
-      <c r="J12" t="n">
-        <v>108.73</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Itú</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Autarquia</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.4958342209485269</v>
-      </c>
-      <c r="E13" t="n">
-        <v>89.78</v>
-      </c>
-      <c r="F13" t="n">
-        <v>33.45</v>
-      </c>
-      <c r="G13" t="n">
-        <v>59.07</v>
-      </c>
-      <c r="H13" t="n">
-        <v>28.58</v>
-      </c>
-      <c r="I13" t="n">
-        <v>85.64</v>
-      </c>
-      <c r="J13" t="n">
-        <v>111.97</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Valinhos</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Autarquia</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.4823263700178126</v>
-      </c>
-      <c r="E14" t="n">
-        <v>96.28</v>
-      </c>
-      <c r="F14" t="n">
-        <v>20.05</v>
-      </c>
-      <c r="G14" t="n">
-        <v>38.58</v>
-      </c>
-      <c r="H14" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="I14" t="n">
-        <v>93.66</v>
-      </c>
-      <c r="J14" t="n">
-        <v>76.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Vinhedo</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Autarquia</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.4816025608815385</v>
-      </c>
-      <c r="E15" t="n">
-        <v>97.11</v>
-      </c>
-      <c r="F15" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="G15" t="n">
-        <v>34.23</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="I15" t="n">
-        <v>89.09</v>
-      </c>
-      <c r="J15" t="n">
-        <v>85.05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Mogi Mirim</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Autarquia</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.4811719604287907</v>
-      </c>
-      <c r="E16" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="F16" t="n">
-        <v>24.85</v>
-      </c>
-      <c r="G16" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="I16" t="n">
-        <v>84.98999999999999</v>
-      </c>
-      <c r="J16" t="n">
-        <v>110.59</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Tietê</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Autarquia</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.4630571034763259</v>
-      </c>
-      <c r="E17" t="n">
-        <v>98.91</v>
-      </c>
-      <c r="F17" t="n">
-        <v>25.17</v>
-      </c>
-      <c r="G17" t="n">
-        <v>37.81</v>
-      </c>
-      <c r="H17" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="I17" t="n">
-        <v>83.98999999999999</v>
-      </c>
-      <c r="J17" t="n">
-        <v>68.19</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Artur Nogueira</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Autarquia</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.4586367685855982</v>
-      </c>
-      <c r="E18" t="n">
-        <v>91.16</v>
-      </c>
-      <c r="F18" t="n">
-        <v>17.68</v>
-      </c>
-      <c r="G18" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="H18" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="I18" t="n">
-        <v>89.94</v>
-      </c>
-      <c r="J18" t="n">
-        <v>67.76000000000001</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Atibaia</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Autarquia</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.3831762242734187</v>
-      </c>
-      <c r="E19" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="F19" t="n">
-        <v>27.23</v>
-      </c>
-      <c r="G19" t="n">
-        <v>36.27</v>
-      </c>
-      <c r="H19" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="I19" t="n">
-        <v>61.02</v>
-      </c>
-      <c r="J19" t="n">
-        <v>64.81</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Salto</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Autarquia</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.2596426385914937</v>
-      </c>
-      <c r="E20" t="n">
-        <v>96.86</v>
-      </c>
-      <c r="F20" t="n">
-        <v>19.47</v>
-      </c>
-      <c r="G20" t="n">
-        <v>38.83</v>
-      </c>
-      <c r="H20" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>96.3</v>
+        <v>91.66</v>
       </c>
     </row>
   </sheetData>
@@ -3970,7 +3648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4027,155 +3705,155 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sumaré</t>
+          <t>Nazaré Paulista</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Empresa privada</t>
+          <t>Sociedade de economia mista</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5139840024875143</v>
+        <v>0.1933944351525965</v>
       </c>
       <c r="E2" t="n">
-        <v>99.56</v>
+        <v>44.48</v>
       </c>
       <c r="F2" t="n">
-        <v>20.52</v>
+        <v>15.31</v>
       </c>
       <c r="G2" t="n">
-        <v>18.58</v>
+        <v>27.71</v>
       </c>
       <c r="H2" t="n">
-        <v>19.4</v>
+        <v>12.84</v>
       </c>
       <c r="I2" t="n">
-        <v>99.56</v>
+        <v>25.28</v>
       </c>
       <c r="J2" t="n">
-        <v>80.12</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Limeira</t>
+          <t>Itapeva</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Empresa privada</t>
+          <t>Sociedade de economia mista</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5056631921207716</v>
+        <v>0.2503795395192028</v>
       </c>
       <c r="E3" t="n">
-        <v>96.98</v>
+        <v>53.85</v>
       </c>
       <c r="F3" t="n">
-        <v>16.45</v>
+        <v>13.77</v>
       </c>
       <c r="G3" t="n">
-        <v>16.58</v>
+        <v>28.17</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>279.82</v>
       </c>
       <c r="I3" t="n">
-        <v>96.98</v>
+        <v>35.67</v>
       </c>
       <c r="J3" t="n">
-        <v>88.06</v>
+        <v>59.98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Santa Gertrudes</t>
+          <t>Jarinú</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Empresa privada</t>
+          <t>Sociedade de economia mista</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4968397909795718</v>
+        <v>0.2509075926898587</v>
       </c>
       <c r="E4" t="n">
-        <v>97.94</v>
+        <v>63.41</v>
       </c>
       <c r="F4" t="n">
-        <v>15.62</v>
+        <v>16.27</v>
       </c>
       <c r="G4" t="n">
-        <v>16.89</v>
+        <v>29.56</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9</v>
+        <v>7.58</v>
       </c>
       <c r="I4" t="n">
-        <v>97.94</v>
+        <v>31.03</v>
       </c>
       <c r="J4" t="n">
-        <v>72.63</v>
+        <v>52.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Holambra</t>
+          <t>Pedra Bela</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Empresa privada</t>
+          <t>Sociedade de economia mista</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4704926443421159</v>
+        <v>0.2519548465686475</v>
       </c>
       <c r="E5" t="n">
-        <v>80.53</v>
+        <v>24.77</v>
       </c>
       <c r="F5" t="n">
-        <v>45.43</v>
+        <v>13.52</v>
       </c>
       <c r="G5" t="n">
-        <v>24.54</v>
+        <v>3.28</v>
       </c>
       <c r="H5" t="n">
-        <v>5.09</v>
+        <v>6.98</v>
       </c>
       <c r="I5" t="n">
-        <v>80.94</v>
+        <v>21.45</v>
       </c>
       <c r="J5" t="n">
-        <v>80</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rio Claro</t>
+          <t>Tuiuti</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4184,61 +3862,205 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4679844097301317</v>
+        <v>0.2544084320848108</v>
       </c>
       <c r="E6" t="n">
-        <v>96.44</v>
+        <v>47.24</v>
       </c>
       <c r="F6" t="n">
-        <v>22.78</v>
+        <v>23.95</v>
       </c>
       <c r="G6" t="n">
-        <v>38.3</v>
+        <v>50.99</v>
       </c>
       <c r="H6" t="n">
-        <v>0.92</v>
+        <v>25.82</v>
       </c>
       <c r="I6" t="n">
-        <v>78.65000000000001</v>
+        <v>39.51</v>
       </c>
       <c r="J6" t="n">
-        <v>99.95999999999999</v>
+        <v>52.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tuiuti</t>
+          <t>Salto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Empresa privada</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2544084320848108</v>
+        <v>0.2596426385914937</v>
       </c>
       <c r="E7" t="n">
-        <v>47.24</v>
+        <v>96.86</v>
       </c>
       <c r="F7" t="n">
-        <v>23.95</v>
+        <v>19.47</v>
       </c>
       <c r="G7" t="n">
-        <v>50.99</v>
+        <v>38.83</v>
       </c>
       <c r="H7" t="n">
-        <v>25.82</v>
+        <v>8.1</v>
       </c>
       <c r="I7" t="n">
-        <v>39.51</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>52.26</v>
+        <v>96.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Vargem</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2753370885178169</v>
+      </c>
+      <c r="E8" t="n">
+        <v>56</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>45.59</v>
+      </c>
+      <c r="J8" t="n">
+        <v>52.06</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>69</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mairiporã</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2759208578629322</v>
+      </c>
+      <c r="E9" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>49.51</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>68</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Camanducaia</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2766337464115645</v>
+      </c>
+      <c r="E10" t="n">
+        <v>56.62</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="G10" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="H10" t="n">
+        <v>194.42</v>
+      </c>
+      <c r="I10" t="n">
+        <v>44.26</v>
+      </c>
+      <c r="J10" t="n">
+        <v>58.09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>67</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pinhalzinho</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2880491516203196</v>
+      </c>
+      <c r="E11" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>64.41</v>
       </c>
     </row>
   </sheetData>
@@ -4252,7 +4074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4313,34 +4135,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cosmópolis</t>
+          <t>Rio das Pedras</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Município</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5457524239468542</v>
+        <v>0.5654832830138814</v>
       </c>
       <c r="E2" t="n">
-        <v>97.47</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>32.79</v>
+        <v>26.84</v>
       </c>
       <c r="G2" t="n">
-        <v>25.02</v>
+        <v>56.97</v>
       </c>
       <c r="H2" t="n">
-        <v>8.35</v>
+        <v>0.6</v>
       </c>
       <c r="I2" t="n">
-        <v>97.47</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>114.51</v>
+        <v>151.49</v>
       </c>
     </row>
     <row r="3">
@@ -4349,34 +4171,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rafard</t>
+          <t>Santa Bárbara D Oeste</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Município</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5192770534226446</v>
+        <v>0.5347131860269471</v>
       </c>
       <c r="E3" t="n">
-        <v>96.84999999999999</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>22.44</v>
+        <v>22.78</v>
       </c>
       <c r="G3" t="n">
-        <v>32.96</v>
+        <v>47.21</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06</v>
+        <v>2.42</v>
       </c>
       <c r="I3" t="n">
-        <v>96.84999999999999</v>
+        <v>99.05</v>
       </c>
       <c r="J3" t="n">
-        <v>70</v>
+        <v>117.02</v>
       </c>
     </row>
     <row r="4">
@@ -4385,34 +4207,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Iracemápolis</t>
+          <t>Piracicaba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Município</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5022116034521068</v>
+        <v>0.5325648407132801</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>92.23</v>
       </c>
       <c r="F4" t="n">
-        <v>31.22</v>
+        <v>27.09</v>
       </c>
       <c r="G4" t="n">
-        <v>15.98</v>
+        <v>50.91</v>
       </c>
       <c r="H4" t="n">
-        <v>0.14</v>
+        <v>8.52</v>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>99.69</v>
       </c>
       <c r="J4" t="n">
-        <v>22.13</v>
+        <v>119.55</v>
       </c>
     </row>
     <row r="5">
@@ -4421,34 +4243,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jaguariúna</t>
+          <t>Dois Córregos</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Município</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4993247936699369</v>
+        <v>0.5300423012009458</v>
       </c>
       <c r="E5" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>20.62</v>
+        <v>20.46</v>
       </c>
       <c r="G5" t="n">
-        <v>30.99</v>
+        <v>42.4</v>
       </c>
       <c r="H5" t="n">
-        <v>9.619999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>96.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="J5" t="n">
-        <v>83.33</v>
+        <v>121.93</v>
       </c>
     </row>
     <row r="6">
@@ -4457,34 +4279,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Itirapina</t>
+          <t>Cordeirópolis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Município</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4919872546028742</v>
+        <v>0.5260104700145199</v>
       </c>
       <c r="E6" t="n">
-        <v>89.52</v>
+        <v>99</v>
       </c>
       <c r="F6" t="n">
-        <v>17.96</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>28.31</v>
+        <v>44.49</v>
       </c>
       <c r="H6" t="n">
-        <v>14.96</v>
+        <v>1.19</v>
       </c>
       <c r="I6" t="n">
-        <v>82.64</v>
+        <v>97.36</v>
       </c>
       <c r="J6" t="n">
-        <v>140.27</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="7">
@@ -4493,34 +4315,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Santo Antônio de Posse</t>
+          <t>Americana</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Município</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4902010290034317</v>
+        <v>0.5219467392588566</v>
       </c>
       <c r="E7" t="n">
-        <v>93.34999999999999</v>
+        <v>99.83</v>
       </c>
       <c r="F7" t="n">
-        <v>22.96</v>
+        <v>31.67</v>
       </c>
       <c r="G7" t="n">
-        <v>38.97</v>
+        <v>58.79</v>
       </c>
       <c r="H7" t="n">
-        <v>0.66</v>
+        <v>45.35</v>
       </c>
       <c r="I7" t="n">
-        <v>93.34999999999999</v>
+        <v>96.84</v>
       </c>
       <c r="J7" t="n">
-        <v>85.28</v>
+        <v>92.01000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -4529,34 +4351,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bom Jesus dos Perdões</t>
+          <t>Pedreira</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Município</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4894050312429654</v>
+        <v>0.5172977231558979</v>
       </c>
       <c r="E8" t="n">
-        <v>92.41</v>
+        <v>98.33</v>
       </c>
       <c r="F8" t="n">
-        <v>21.5</v>
+        <v>29.38</v>
       </c>
       <c r="G8" t="n">
-        <v>9.74</v>
+        <v>58.36</v>
       </c>
       <c r="H8" t="n">
-        <v>3.63</v>
+        <v>52.05</v>
       </c>
       <c r="I8" t="n">
-        <v>92.41</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>64.45</v>
+        <v>91.66</v>
       </c>
     </row>
     <row r="9">
@@ -4565,34 +4387,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ipeúna</t>
+          <t>Engenheiro Coelho</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Município</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.4768787316305536</v>
+        <v>0.5165540506893349</v>
       </c>
       <c r="E9" t="n">
-        <v>92.78</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>14.85</v>
+        <v>19.12</v>
       </c>
       <c r="G9" t="n">
-        <v>14.81</v>
+        <v>44.16</v>
       </c>
       <c r="H9" t="n">
-        <v>2.44</v>
+        <v>1.33</v>
       </c>
       <c r="I9" t="n">
-        <v>84.94</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>98.69</v>
+        <v>126.43</v>
       </c>
     </row>
     <row r="10">
@@ -4601,34 +4423,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Louveira</t>
+          <t>Capivari</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Município</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.4494362706740235</v>
+        <v>0.5081899659912953</v>
       </c>
       <c r="E10" t="n">
-        <v>90.93000000000001</v>
+        <v>96.25</v>
       </c>
       <c r="F10" t="n">
-        <v>24.89</v>
+        <v>26.13</v>
       </c>
       <c r="G10" t="n">
-        <v>23.43</v>
+        <v>38.16</v>
       </c>
       <c r="H10" t="n">
-        <v>9.1</v>
+        <v>6.11</v>
       </c>
       <c r="I10" t="n">
-        <v>78.68000000000001</v>
+        <v>96.25</v>
       </c>
       <c r="J10" t="n">
-        <v>78.19</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -4637,34 +4459,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Analândia</t>
+          <t>Indaiatuba</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Município</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.4009111521091335</v>
+        <v>0.5072676042789033</v>
       </c>
       <c r="E11" t="n">
-        <v>84.91</v>
+        <v>95.09</v>
       </c>
       <c r="F11" t="n">
-        <v>18.9</v>
+        <v>23.31</v>
       </c>
       <c r="G11" t="n">
-        <v>90.09</v>
+        <v>38.95</v>
       </c>
       <c r="H11" t="n">
-        <v>5.83</v>
+        <v>6.29</v>
       </c>
       <c r="I11" t="n">
-        <v>68.31999999999999</v>
+        <v>94.41</v>
       </c>
       <c r="J11" t="n">
-        <v>85.19</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="12">
@@ -4673,34 +4495,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Corumbataí</t>
+          <t>Brotas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Município</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.3899070793566656</v>
+        <v>0.4964879726116124</v>
       </c>
       <c r="E12" t="n">
-        <v>76.92</v>
+        <v>92.12</v>
       </c>
       <c r="F12" t="n">
-        <v>24.04</v>
+        <v>22.02</v>
       </c>
       <c r="G12" t="n">
-        <v>46.54</v>
+        <v>29.39</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06</v>
+        <v>14.1</v>
       </c>
       <c r="I12" t="n">
-        <v>64.67</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>48.11</v>
+        <v>108.73</v>
       </c>
     </row>
     <row r="13">
@@ -4709,34 +4531,286 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Monte Alegre do Sul</t>
+          <t>Itú</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Município</t>
+          <t>Autarquia</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.3620214003790248</v>
+        <v>0.4958342209485269</v>
       </c>
       <c r="E13" t="n">
-        <v>92.84999999999999</v>
+        <v>89.78</v>
       </c>
       <c r="F13" t="n">
-        <v>40.14</v>
+        <v>33.45</v>
       </c>
       <c r="G13" t="n">
-        <v>86.08</v>
+        <v>59.07</v>
       </c>
       <c r="H13" t="n">
-        <v>7.22</v>
+        <v>28.58</v>
       </c>
       <c r="I13" t="n">
-        <v>47.13</v>
+        <v>85.64</v>
       </c>
       <c r="J13" t="n">
-        <v>47.13</v>
+        <v>111.97</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Valinhos</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Autarquia</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4823263700178126</v>
+      </c>
+      <c r="E14" t="n">
+        <v>96.28</v>
+      </c>
+      <c r="F14" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="H14" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="I14" t="n">
+        <v>93.66</v>
+      </c>
+      <c r="J14" t="n">
+        <v>76.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Vinhedo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Autarquia</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.4816025608815385</v>
+      </c>
+      <c r="E15" t="n">
+        <v>97.11</v>
+      </c>
+      <c r="F15" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="G15" t="n">
+        <v>34.23</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="J15" t="n">
+        <v>85.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mogi Mirim</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Autarquia</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.4811719604287907</v>
+      </c>
+      <c r="E16" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="G16" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="I16" t="n">
+        <v>84.98999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>110.59</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tietê</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Autarquia</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.4630571034763259</v>
+      </c>
+      <c r="E17" t="n">
+        <v>98.91</v>
+      </c>
+      <c r="F17" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="G17" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="H17" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="I17" t="n">
+        <v>83.98999999999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>68.19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Artur Nogueira</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Autarquia</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.4586367685855982</v>
+      </c>
+      <c r="E18" t="n">
+        <v>91.16</v>
+      </c>
+      <c r="F18" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="G18" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="I18" t="n">
+        <v>89.94</v>
+      </c>
+      <c r="J18" t="n">
+        <v>67.76000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Atibaia</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Autarquia</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.3831762242734187</v>
+      </c>
+      <c r="E19" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="G19" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="H19" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="J19" t="n">
+        <v>64.81</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Salto</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Autarquia</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2596426385914937</v>
+      </c>
+      <c r="E20" t="n">
+        <v>96.86</v>
+      </c>
+      <c r="F20" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="G20" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>96.3</v>
       </c>
     </row>
   </sheetData>
@@ -4750,7 +4824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4811,34 +4885,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Águas de São Pedro</t>
+          <t>Sumaré</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sociedade de economia mista</t>
+          <t>Empresa privada</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5680751715371495</v>
+        <v>0.5139840024875143</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>99.56</v>
       </c>
       <c r="F2" t="n">
-        <v>18.09</v>
+        <v>20.52</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9</v>
+        <v>18.58</v>
       </c>
       <c r="H2" t="n">
-        <v>9.35</v>
+        <v>19.4</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>99.56</v>
       </c>
       <c r="J2" t="n">
-        <v>94.06</v>
+        <v>80.12</v>
       </c>
     </row>
     <row r="3">
@@ -4847,34 +4921,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hortolândia</t>
+          <t>Limeira</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sociedade de economia mista</t>
+          <t>Empresa privada</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5155802240655301</v>
+        <v>0.5056631921207716</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>96.98</v>
       </c>
       <c r="F3" t="n">
-        <v>16.32</v>
+        <v>16.45</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>16.58</v>
       </c>
       <c r="H3" t="n">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>98.61</v>
+        <v>96.98</v>
       </c>
       <c r="J3" t="n">
-        <v>94</v>
+        <v>88.06</v>
       </c>
     </row>
     <row r="4">
@@ -4883,34 +4957,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jundiaí</t>
+          <t>Santa Gertrudes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sociedade de economia mista</t>
+          <t>Empresa privada</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5141586697424484</v>
+        <v>0.4968397909795718</v>
       </c>
       <c r="E4" t="n">
-        <v>98.56999999999999</v>
+        <v>97.94</v>
       </c>
       <c r="F4" t="n">
-        <v>22.44</v>
+        <v>15.62</v>
       </c>
       <c r="G4" t="n">
-        <v>26.43</v>
+        <v>16.89</v>
       </c>
       <c r="H4" t="n">
-        <v>8.06</v>
+        <v>1.9</v>
       </c>
       <c r="I4" t="n">
-        <v>96.56</v>
+        <v>97.94</v>
       </c>
       <c r="J4" t="n">
-        <v>94.78</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="5">
@@ -4919,34 +4993,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nova Odessa</t>
+          <t>Holambra</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sociedade de economia mista</t>
+          <t>Empresa privada</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.5127737056159185</v>
+        <v>0.4704926443421159</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>80.53</v>
       </c>
       <c r="F5" t="n">
-        <v>17.41</v>
+        <v>45.43</v>
       </c>
       <c r="G5" t="n">
-        <v>27.97</v>
+        <v>24.54</v>
       </c>
       <c r="H5" t="n">
-        <v>1.22</v>
+        <v>5.09</v>
       </c>
       <c r="I5" t="n">
-        <v>98</v>
+        <v>80.94</v>
       </c>
       <c r="J5" t="n">
-        <v>94.31999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -4955,34 +5029,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Paulínia</t>
+          <t>Rio Claro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sociedade de economia mista</t>
+          <t>Empresa privada</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5125610382792181</v>
+        <v>0.4679844097301317</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>96.44</v>
       </c>
       <c r="F6" t="n">
-        <v>18.81</v>
+        <v>22.78</v>
       </c>
       <c r="G6" t="n">
-        <v>22.43</v>
+        <v>38.3</v>
       </c>
       <c r="H6" t="n">
-        <v>5.93</v>
+        <v>0.92</v>
       </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>82.61</v>
+        <v>99.95999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -4991,1222 +5065,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Campinas</t>
+          <t>Tuiuti</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sociedade de economia mista</t>
+          <t>Empresa privada</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5095624877102957</v>
+        <v>0.2544084320848108</v>
       </c>
       <c r="E7" t="n">
-        <v>99.8</v>
+        <v>47.24</v>
       </c>
       <c r="F7" t="n">
-        <v>15.65</v>
+        <v>23.95</v>
       </c>
       <c r="G7" t="n">
-        <v>17.46</v>
+        <v>50.99</v>
       </c>
       <c r="H7" t="n">
-        <v>3.27</v>
+        <v>25.82</v>
       </c>
       <c r="I7" t="n">
-        <v>96.61</v>
+        <v>39.51</v>
       </c>
       <c r="J7" t="n">
-        <v>91.20999999999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Botucatu</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.5042192403128086</v>
-      </c>
-      <c r="E8" t="n">
-        <v>99.06999999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="H8" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="I8" t="n">
-        <v>96.51000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>93.65000000000001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Santa Maria da Serra</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.4876762828092646</v>
-      </c>
-      <c r="E9" t="n">
-        <v>88.45</v>
-      </c>
-      <c r="F9" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="G9" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="I9" t="n">
-        <v>92.72</v>
-      </c>
-      <c r="J9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Mombuca</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.4780672713580246</v>
-      </c>
-      <c r="E10" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="F10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>15.95</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="I10" t="n">
-        <v>86.11</v>
-      </c>
-      <c r="J10" t="n">
-        <v>99.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Monte Mor</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.4776256351355191</v>
-      </c>
-      <c r="E11" t="n">
-        <v>100</v>
-      </c>
-      <c r="F11" t="n">
-        <v>16.43</v>
-      </c>
-      <c r="G11" t="n">
-        <v>26.54</v>
-      </c>
-      <c r="H11" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>89.11</v>
-      </c>
-      <c r="J11" t="n">
-        <v>80.51000000000001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Várzea Paulista</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.4750240494496366</v>
-      </c>
-      <c r="E12" t="n">
-        <v>94.42</v>
-      </c>
-      <c r="F12" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="G12" t="n">
-        <v>27.21</v>
-      </c>
-      <c r="H12" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>88.43000000000001</v>
-      </c>
-      <c r="J12" t="n">
-        <v>90.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Amparo</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.4744316225057632</v>
-      </c>
-      <c r="E13" t="n">
-        <v>92.23</v>
-      </c>
-      <c r="F13" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="G13" t="n">
-        <v>39.49</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I13" t="n">
-        <v>87.62</v>
-      </c>
-      <c r="J13" t="n">
-        <v>87.75</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Torrinha</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.4732778096094423</v>
-      </c>
-      <c r="E14" t="n">
-        <v>93.34</v>
-      </c>
-      <c r="F14" t="n">
-        <v>16.92</v>
-      </c>
-      <c r="G14" t="n">
-        <v>30.46</v>
-      </c>
-      <c r="H14" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="I14" t="n">
-        <v>90.52</v>
-      </c>
-      <c r="J14" t="n">
-        <v>84.51000000000001</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Morungaba</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.4692542180207449</v>
-      </c>
-      <c r="E15" t="n">
-        <v>87.75</v>
-      </c>
-      <c r="F15" t="n">
-        <v>16.29</v>
-      </c>
-      <c r="G15" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="I15" t="n">
-        <v>85.33</v>
-      </c>
-      <c r="J15" t="n">
-        <v>106.91</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Itatiba</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.4679933451099388</v>
-      </c>
-      <c r="E16" t="n">
-        <v>92.59</v>
-      </c>
-      <c r="F16" t="n">
-        <v>18.45</v>
-      </c>
-      <c r="G16" t="n">
-        <v>30.53</v>
-      </c>
-      <c r="H16" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="J16" t="n">
-        <v>89.94</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Saltinho</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.4678991630603713</v>
-      </c>
-      <c r="E17" t="n">
-        <v>88.06999999999999</v>
-      </c>
-      <c r="F17" t="n">
-        <v>16.05</v>
-      </c>
-      <c r="G17" t="n">
-        <v>24.51</v>
-      </c>
-      <c r="H17" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="I17" t="n">
-        <v>84.78</v>
-      </c>
-      <c r="J17" t="n">
-        <v>105.83</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Bragança Paulista</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.4496681051973613</v>
-      </c>
-      <c r="E18" t="n">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="F18" t="n">
-        <v>15.31</v>
-      </c>
-      <c r="G18" t="n">
-        <v>22.01</v>
-      </c>
-      <c r="H18" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>83.06999999999999</v>
-      </c>
-      <c r="J18" t="n">
-        <v>70.95</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Elias Fausto</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.446299503192475</v>
-      </c>
-      <c r="E19" t="n">
-        <v>83.97</v>
-      </c>
-      <c r="F19" t="n">
-        <v>15.77</v>
-      </c>
-      <c r="G19" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="H19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="I19" t="n">
-        <v>79.06</v>
-      </c>
-      <c r="J19" t="n">
-        <v>100.55</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Charqueada</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.4451233570692567</v>
-      </c>
-      <c r="E20" t="n">
-        <v>99.05</v>
-      </c>
-      <c r="F20" t="n">
-        <v>16.66</v>
-      </c>
-      <c r="G20" t="n">
-        <v>24.18</v>
-      </c>
-      <c r="H20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I20" t="n">
-        <v>79.45</v>
-      </c>
-      <c r="J20" t="n">
-        <v>70.06</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Anhembi</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.4418598067359545</v>
-      </c>
-      <c r="E21" t="n">
-        <v>85.14</v>
-      </c>
-      <c r="F21" t="n">
-        <v>13.16</v>
-      </c>
-      <c r="G21" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="H21" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="I21" t="n">
-        <v>77.70999999999999</v>
-      </c>
-      <c r="J21" t="n">
-        <v>105.17</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>São Pedro</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0.4395880313520413</v>
-      </c>
-      <c r="E22" t="n">
-        <v>82.70999999999999</v>
-      </c>
-      <c r="F22" t="n">
-        <v>22.55</v>
-      </c>
-      <c r="G22" t="n">
-        <v>57.71</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="I22" t="n">
-        <v>78.98999999999999</v>
-      </c>
-      <c r="J22" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Itupeva</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.4206696316873202</v>
-      </c>
-      <c r="E23" t="n">
-        <v>84.58</v>
-      </c>
-      <c r="F23" t="n">
-        <v>17.76</v>
-      </c>
-      <c r="G23" t="n">
-        <v>20.53</v>
-      </c>
-      <c r="H23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I23" t="n">
-        <v>74.54000000000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>78.56</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Cabreúva</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.420629244860268</v>
-      </c>
-      <c r="E24" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="F24" t="n">
-        <v>18.46</v>
-      </c>
-      <c r="G24" t="n">
-        <v>25.59</v>
-      </c>
-      <c r="H24" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="J24" t="n">
-        <v>79.72</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Campo Limpo Paulista</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0.4134502935390508</v>
-      </c>
-      <c r="E25" t="n">
-        <v>82.43000000000001</v>
-      </c>
-      <c r="F25" t="n">
-        <v>18.47</v>
-      </c>
-      <c r="G25" t="n">
-        <v>12.35</v>
-      </c>
-      <c r="H25" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>68.88</v>
-      </c>
-      <c r="J25" t="n">
-        <v>78.16</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Toledo</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0.4097941594666012</v>
-      </c>
-      <c r="E26" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="F26" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="G26" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="H26" t="n">
-        <v>192.39</v>
-      </c>
-      <c r="I26" t="n">
-        <v>91.78</v>
-      </c>
-      <c r="J26" t="n">
-        <v>85.36</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Serra Negra</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0.3883639908353363</v>
-      </c>
-      <c r="E27" t="n">
-        <v>77.63</v>
-      </c>
-      <c r="F27" t="n">
-        <v>15.95</v>
-      </c>
-      <c r="G27" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="H27" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>65.56</v>
-      </c>
-      <c r="J27" t="n">
-        <v>80.84</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Joanópolis</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0.3832448575407101</v>
-      </c>
-      <c r="E28" t="n">
-        <v>74.59</v>
-      </c>
-      <c r="F28" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="G28" t="n">
-        <v>13.02</v>
-      </c>
-      <c r="H28" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="I28" t="n">
-        <v>67.13</v>
-      </c>
-      <c r="J28" t="n">
-        <v>72.15000000000001</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Piracaia</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0.3391537550334465</v>
-      </c>
-      <c r="E29" t="n">
-        <v>74.13</v>
-      </c>
-      <c r="F29" t="n">
-        <v>15.24</v>
-      </c>
-      <c r="G29" t="n">
-        <v>29</v>
-      </c>
-      <c r="H29" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="I29" t="n">
-        <v>57.64</v>
-      </c>
-      <c r="J29" t="n">
-        <v>59.56</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Sapucaí-Mirim</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0.3375262327432809</v>
-      </c>
-      <c r="E30" t="n">
-        <v>69.39</v>
-      </c>
-      <c r="F30" t="n">
-        <v>12.63</v>
-      </c>
-      <c r="G30" t="n">
-        <v>25.26</v>
-      </c>
-      <c r="H30" t="n">
-        <v>170.53</v>
-      </c>
-      <c r="I30" t="n">
-        <v>58.76</v>
-      </c>
-      <c r="J30" t="n">
-        <v>66.58</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Socorro</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.3217485314950557</v>
-      </c>
-      <c r="E31" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="F31" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="G31" t="n">
-        <v>25.81</v>
-      </c>
-      <c r="H31" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="I31" t="n">
-        <v>54.81</v>
-      </c>
-      <c r="J31" t="n">
-        <v>71.45999999999999</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Extrema</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0.2930568715896419</v>
-      </c>
-      <c r="E32" t="n">
-        <v>58.24</v>
-      </c>
-      <c r="F32" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="G32" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="H32" t="n">
-        <v>259.46</v>
-      </c>
-      <c r="I32" t="n">
-        <v>46.03</v>
-      </c>
-      <c r="J32" t="n">
-        <v>62.45</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Pinhalzinho</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0.2880491516203196</v>
-      </c>
-      <c r="E33" t="n">
-        <v>58.78</v>
-      </c>
-      <c r="F33" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="G33" t="n">
-        <v>23.69</v>
-      </c>
-      <c r="H33" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="J33" t="n">
-        <v>64.41</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Camanducaia</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0.2766337464115645</v>
-      </c>
-      <c r="E34" t="n">
-        <v>56.62</v>
-      </c>
-      <c r="F34" t="n">
-        <v>15.89</v>
-      </c>
-      <c r="G34" t="n">
-        <v>32.86</v>
-      </c>
-      <c r="H34" t="n">
-        <v>194.42</v>
-      </c>
-      <c r="I34" t="n">
-        <v>44.26</v>
-      </c>
-      <c r="J34" t="n">
-        <v>58.09</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Mairiporã</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>0.2759208578629322</v>
-      </c>
-      <c r="E35" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="F35" t="n">
-        <v>17.47</v>
-      </c>
-      <c r="G35" t="n">
-        <v>25.27</v>
-      </c>
-      <c r="H35" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="I35" t="n">
-        <v>40.12</v>
-      </c>
-      <c r="J35" t="n">
-        <v>49.51</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Vargem</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>0.2753370885178169</v>
-      </c>
-      <c r="E36" t="n">
-        <v>56</v>
-      </c>
-      <c r="F36" t="n">
-        <v>15.18</v>
-      </c>
-      <c r="G36" t="n">
-        <v>27.59</v>
-      </c>
-      <c r="H36" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="I36" t="n">
-        <v>45.59</v>
-      </c>
-      <c r="J36" t="n">
-        <v>52.06</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Pedra Bela</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>0.2519548465686475</v>
-      </c>
-      <c r="E37" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="F37" t="n">
-        <v>13.52</v>
-      </c>
-      <c r="G37" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="H37" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="I37" t="n">
-        <v>21.45</v>
-      </c>
-      <c r="J37" t="n">
-        <v>62.17</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Jarinú</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>0.2509075926898587</v>
-      </c>
-      <c r="E38" t="n">
-        <v>63.41</v>
-      </c>
-      <c r="F38" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="G38" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="H38" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="I38" t="n">
-        <v>31.03</v>
-      </c>
-      <c r="J38" t="n">
-        <v>52.25</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Itapeva</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>0.2503795395192028</v>
-      </c>
-      <c r="E39" t="n">
-        <v>53.85</v>
-      </c>
-      <c r="F39" t="n">
-        <v>13.77</v>
-      </c>
-      <c r="G39" t="n">
-        <v>28.17</v>
-      </c>
-      <c r="H39" t="n">
-        <v>279.82</v>
-      </c>
-      <c r="I39" t="n">
-        <v>35.67</v>
-      </c>
-      <c r="J39" t="n">
-        <v>59.98</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Nazaré Paulista</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>0.1933944351525965</v>
-      </c>
-      <c r="E40" t="n">
-        <v>44.48</v>
-      </c>
-      <c r="F40" t="n">
-        <v>15.31</v>
-      </c>
-      <c r="G40" t="n">
-        <v>27.71</v>
-      </c>
-      <c r="H40" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="I40" t="n">
-        <v>25.28</v>
-      </c>
-      <c r="J40" t="n">
-        <v>35.35</v>
+        <v>52.26</v>
       </c>
     </row>
   </sheetData>
@@ -6220,6 +5106,1974 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Posição</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Natureza Jurídica</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>IAG0001</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>IAG2008</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>IAG2013</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>IAG3008</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>IES0001</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>IES2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cosmópolis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5457524239468542</v>
+      </c>
+      <c r="E2" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="G2" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="I2" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="J2" t="n">
+        <v>114.51</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rafard</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5192770534226446</v>
+      </c>
+      <c r="E3" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="G3" t="n">
+        <v>32.96</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I3" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="J3" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Iracemápolis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5022116034521068</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="G4" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jaguariúna</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4993247936699369</v>
+      </c>
+      <c r="E5" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>83.33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Itirapina</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4919872546028742</v>
+      </c>
+      <c r="E6" t="n">
+        <v>89.52</v>
+      </c>
+      <c r="F6" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28.31</v>
+      </c>
+      <c r="H6" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="I6" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="J6" t="n">
+        <v>140.27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Santo Antônio de Posse</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4902010290034317</v>
+      </c>
+      <c r="E7" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="G7" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I7" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>85.28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bom Jesus dos Perdões</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4894050312429654</v>
+      </c>
+      <c r="E8" t="n">
+        <v>92.41</v>
+      </c>
+      <c r="F8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="I8" t="n">
+        <v>92.41</v>
+      </c>
+      <c r="J8" t="n">
+        <v>64.45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ipeúna</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4768787316305536</v>
+      </c>
+      <c r="E9" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I9" t="n">
+        <v>84.94</v>
+      </c>
+      <c r="J9" t="n">
+        <v>98.69</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Louveira</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4494362706740235</v>
+      </c>
+      <c r="E10" t="n">
+        <v>90.93000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="G10" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>78.68000000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>78.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Analândia</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4009111521091335</v>
+      </c>
+      <c r="E11" t="n">
+        <v>84.91</v>
+      </c>
+      <c r="F11" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>90.09</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="I11" t="n">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>85.19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Corumbataí</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3899070793566656</v>
+      </c>
+      <c r="E12" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="F12" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I12" t="n">
+        <v>64.67</v>
+      </c>
+      <c r="J12" t="n">
+        <v>48.11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Monte Alegre do Sul</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3620214003790248</v>
+      </c>
+      <c r="E13" t="n">
+        <v>92.84999999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="G13" t="n">
+        <v>86.08</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="I13" t="n">
+        <v>47.13</v>
+      </c>
+      <c r="J13" t="n">
+        <v>47.13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Posição</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Município</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Natureza Jurídica</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>IAG0001</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>IAG2008</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>IAG2013</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>IAG3008</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>IES0001</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>IES2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Águas de São Pedro</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5680751715371495</v>
+      </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="n">
+        <v>18.09</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>94.06</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hortolândia</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5155802240655301</v>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>98.61</v>
+      </c>
+      <c r="J3" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jundiaí</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5141586697424484</v>
+      </c>
+      <c r="E4" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="G4" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="I4" t="n">
+        <v>96.56</v>
+      </c>
+      <c r="J4" t="n">
+        <v>94.78</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nova Odessa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5127737056159185</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="G5" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I5" t="n">
+        <v>98</v>
+      </c>
+      <c r="J5" t="n">
+        <v>94.31999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Paulínia</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5125610382792181</v>
+      </c>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="I6" t="n">
+        <v>100</v>
+      </c>
+      <c r="J6" t="n">
+        <v>82.61</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Campinas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5095624877102957</v>
+      </c>
+      <c r="E7" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="I7" t="n">
+        <v>96.61</v>
+      </c>
+      <c r="J7" t="n">
+        <v>91.20999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Botucatu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5042192403128086</v>
+      </c>
+      <c r="E8" t="n">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="H8" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="I8" t="n">
+        <v>96.51000000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>93.65000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Maria da Serra</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4876762828092646</v>
+      </c>
+      <c r="E9" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="G9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="I9" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="J9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mombuca</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4780672713580246</v>
+      </c>
+      <c r="E10" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="I10" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="J10" t="n">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Monte Mor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4776256351355191</v>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="G11" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>89.11</v>
+      </c>
+      <c r="J11" t="n">
+        <v>80.51000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Várzea Paulista</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4750240494496366</v>
+      </c>
+      <c r="E12" t="n">
+        <v>94.42</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="G12" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>88.43000000000001</v>
+      </c>
+      <c r="J12" t="n">
+        <v>90.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Amparo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4744316225057632</v>
+      </c>
+      <c r="E13" t="n">
+        <v>92.23</v>
+      </c>
+      <c r="F13" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="G13" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I13" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="J13" t="n">
+        <v>87.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Torrinha</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4732778096094423</v>
+      </c>
+      <c r="E14" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="G14" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="I14" t="n">
+        <v>90.52</v>
+      </c>
+      <c r="J14" t="n">
+        <v>84.51000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Morungaba</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.4692542180207449</v>
+      </c>
+      <c r="E15" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="F15" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="G15" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="I15" t="n">
+        <v>85.33</v>
+      </c>
+      <c r="J15" t="n">
+        <v>106.91</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Itatiba</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.4679933451099388</v>
+      </c>
+      <c r="E16" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="G16" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>89.94</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Saltinho</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.4678991630603713</v>
+      </c>
+      <c r="E17" t="n">
+        <v>88.06999999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="G17" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="I17" t="n">
+        <v>84.78</v>
+      </c>
+      <c r="J17" t="n">
+        <v>105.83</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bragança Paulista</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.4496681051973613</v>
+      </c>
+      <c r="E18" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="G18" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>83.06999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>70.95</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Elias Fausto</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.446299503192475</v>
+      </c>
+      <c r="E19" t="n">
+        <v>83.97</v>
+      </c>
+      <c r="F19" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="G19" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="I19" t="n">
+        <v>79.06</v>
+      </c>
+      <c r="J19" t="n">
+        <v>100.55</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Charqueada</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.4451233570692567</v>
+      </c>
+      <c r="E20" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="F20" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="G20" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="J20" t="n">
+        <v>70.06</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Anhembi</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.4418598067359545</v>
+      </c>
+      <c r="E21" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="F21" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="G21" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="I21" t="n">
+        <v>77.70999999999999</v>
+      </c>
+      <c r="J21" t="n">
+        <v>105.17</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>São Pedro</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.4395880313520413</v>
+      </c>
+      <c r="E22" t="n">
+        <v>82.70999999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="G22" t="n">
+        <v>57.71</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="I22" t="n">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Itupeva</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.4206696316873202</v>
+      </c>
+      <c r="E23" t="n">
+        <v>84.58</v>
+      </c>
+      <c r="F23" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>74.54000000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>78.56</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Cabreúva</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.420629244860268</v>
+      </c>
+      <c r="E24" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="F24" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="G24" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>79.72</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Campo Limpo Paulista</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.4134502935390508</v>
+      </c>
+      <c r="E25" t="n">
+        <v>82.43000000000001</v>
+      </c>
+      <c r="F25" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="G25" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="I25" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="J25" t="n">
+        <v>78.16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4097941594666012</v>
+      </c>
+      <c r="E26" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="G26" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="H26" t="n">
+        <v>192.39</v>
+      </c>
+      <c r="I26" t="n">
+        <v>91.78</v>
+      </c>
+      <c r="J26" t="n">
+        <v>85.36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Serra Negra</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.3883639908353363</v>
+      </c>
+      <c r="E27" t="n">
+        <v>77.63</v>
+      </c>
+      <c r="F27" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="G27" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="H27" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="I27" t="n">
+        <v>65.56</v>
+      </c>
+      <c r="J27" t="n">
+        <v>80.84</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Joanópolis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3832448575407101</v>
+      </c>
+      <c r="E28" t="n">
+        <v>74.59</v>
+      </c>
+      <c r="F28" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="G28" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="I28" t="n">
+        <v>67.13</v>
+      </c>
+      <c r="J28" t="n">
+        <v>72.15000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Piracaia</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.3391537550334465</v>
+      </c>
+      <c r="E29" t="n">
+        <v>74.13</v>
+      </c>
+      <c r="F29" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="G29" t="n">
+        <v>29</v>
+      </c>
+      <c r="H29" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="I29" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="J29" t="n">
+        <v>59.56</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sapucaí-Mirim</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.3375262327432809</v>
+      </c>
+      <c r="E30" t="n">
+        <v>69.39</v>
+      </c>
+      <c r="F30" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="G30" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="H30" t="n">
+        <v>170.53</v>
+      </c>
+      <c r="I30" t="n">
+        <v>58.76</v>
+      </c>
+      <c r="J30" t="n">
+        <v>66.58</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Socorro</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.3217485314950557</v>
+      </c>
+      <c r="E31" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="H31" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="I31" t="n">
+        <v>54.81</v>
+      </c>
+      <c r="J31" t="n">
+        <v>71.45999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Extrema</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.2930568715896419</v>
+      </c>
+      <c r="E32" t="n">
+        <v>58.24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="G32" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="H32" t="n">
+        <v>259.46</v>
+      </c>
+      <c r="I32" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="J32" t="n">
+        <v>62.45</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pinhalzinho</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.2880491516203196</v>
+      </c>
+      <c r="E33" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="G33" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="J33" t="n">
+        <v>64.41</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Camanducaia</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.2766337464115645</v>
+      </c>
+      <c r="E34" t="n">
+        <v>56.62</v>
+      </c>
+      <c r="F34" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="G34" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="H34" t="n">
+        <v>194.42</v>
+      </c>
+      <c r="I34" t="n">
+        <v>44.26</v>
+      </c>
+      <c r="J34" t="n">
+        <v>58.09</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Mairiporã</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.2759208578629322</v>
+      </c>
+      <c r="E35" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="F35" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="G35" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="H35" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I35" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="J35" t="n">
+        <v>49.51</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Vargem</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.2753370885178169</v>
+      </c>
+      <c r="E36" t="n">
+        <v>56</v>
+      </c>
+      <c r="F36" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="G36" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="H36" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="I36" t="n">
+        <v>45.59</v>
+      </c>
+      <c r="J36" t="n">
+        <v>52.06</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pedra Bela</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.2519548465686475</v>
+      </c>
+      <c r="E37" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="F37" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="H37" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="I37" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="J37" t="n">
+        <v>62.17</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Jarinú</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.2509075926898587</v>
+      </c>
+      <c r="E38" t="n">
+        <v>63.41</v>
+      </c>
+      <c r="F38" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="G38" t="n">
+        <v>29.56</v>
+      </c>
+      <c r="H38" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="I38" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="J38" t="n">
+        <v>52.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Itapeva</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.2503795395192028</v>
+      </c>
+      <c r="E39" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="F39" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="G39" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="H39" t="n">
+        <v>279.82</v>
+      </c>
+      <c r="I39" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="J39" t="n">
+        <v>59.98</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Nazaré Paulista</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.1933944351525965</v>
+      </c>
+      <c r="E40" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="F40" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="G40" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="H40" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="I40" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="J40" t="n">
+        <v>35.35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/SAW-analytics/src/dados/resultado/ranking_saw_pcj_2024.xlsx
+++ b/SAW-analytics/src/dados/resultado/ranking_saw_pcj_2024.xlsx
@@ -57,8 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -503,8 +504,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.5680751715371495</v>
+      <c r="E2" s="1" t="n">
+        <v>0.57</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -544,8 +545,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.5654832830138814</v>
+      <c r="E3" s="1" t="n">
+        <v>0.57</v>
       </c>
       <c r="F3" t="n">
         <v>96.23999999999999</v>
@@ -585,8 +586,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.5457524239468542</v>
+      <c r="E4" s="1" t="n">
+        <v>0.55</v>
       </c>
       <c r="F4" t="n">
         <v>97.47</v>
@@ -626,8 +627,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.5347131860269471</v>
+      <c r="E5" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F5" t="n">
         <v>99.43000000000001</v>
@@ -667,8 +668,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0.5325648407132801</v>
+      <c r="E6" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F6" t="n">
         <v>92.23</v>
@@ -708,8 +709,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.5300423012009458</v>
+      <c r="E7" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F7" t="n">
         <v>100</v>
@@ -749,8 +750,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.5260104700145199</v>
+      <c r="E8" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F8" t="n">
         <v>99</v>
@@ -790,8 +791,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0.5219467392588566</v>
+      <c r="E9" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F9" t="n">
         <v>99.83</v>
@@ -831,8 +832,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0.5192770534226446</v>
+      <c r="E10" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F10" t="n">
         <v>96.84999999999999</v>
@@ -872,8 +873,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0.5172977231558979</v>
+      <c r="E11" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F11" t="n">
         <v>98.33</v>
@@ -913,8 +914,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>0.5165540506893349</v>
+      <c r="E12" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F12" t="n">
         <v>94.06999999999999</v>
@@ -954,8 +955,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>0.5155802240655301</v>
+      <c r="E13" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F13" t="n">
         <v>100</v>
@@ -995,8 +996,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>0.5141586697424484</v>
+      <c r="E14" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F14" t="n">
         <v>98.56999999999999</v>
@@ -1036,8 +1037,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>0.5139840024875143</v>
+      <c r="E15" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F15" t="n">
         <v>99.56</v>
@@ -1077,8 +1078,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0.5127737056159185</v>
+      <c r="E16" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F16" t="n">
         <v>100</v>
@@ -1118,8 +1119,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>0.5125610382792181</v>
+      <c r="E17" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F17" t="n">
         <v>100</v>
@@ -1159,8 +1160,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>0.5095624877102957</v>
+      <c r="E18" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F18" t="n">
         <v>99.8</v>
@@ -1200,8 +1201,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>0.5081899659912953</v>
+      <c r="E19" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F19" t="n">
         <v>96.25</v>
@@ -1241,8 +1242,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>0.5072676042789033</v>
+      <c r="E20" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F20" t="n">
         <v>95.09</v>
@@ -1282,8 +1283,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>0.5056631921207716</v>
+      <c r="E21" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F21" t="n">
         <v>96.98</v>
@@ -1323,8 +1324,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>0.5042192403128086</v>
+      <c r="E22" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F22" t="n">
         <v>99.06999999999999</v>
@@ -1364,8 +1365,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>0.5022116034521068</v>
+      <c r="E23" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F23" t="n">
         <v>100</v>
@@ -1405,8 +1406,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>0.4993247936699369</v>
+      <c r="E24" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F24" t="n">
         <v>96.90000000000001</v>
@@ -1446,8 +1447,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>0.4968397909795718</v>
+      <c r="E25" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F25" t="n">
         <v>97.94</v>
@@ -1487,8 +1488,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>0.4964879726116124</v>
+      <c r="E26" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F26" t="n">
         <v>92.12</v>
@@ -1528,8 +1529,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>0.4958342209485269</v>
+      <c r="E27" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F27" t="n">
         <v>89.78</v>
@@ -1569,8 +1570,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>0.4919872546028742</v>
+      <c r="E28" s="1" t="n">
+        <v>0.49</v>
       </c>
       <c r="F28" t="n">
         <v>89.52</v>
@@ -1610,8 +1611,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>0.4902010290034317</v>
+      <c r="E29" s="1" t="n">
+        <v>0.49</v>
       </c>
       <c r="F29" t="n">
         <v>93.34999999999999</v>
@@ -1651,8 +1652,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>0.4894050312429654</v>
+      <c r="E30" s="1" t="n">
+        <v>0.49</v>
       </c>
       <c r="F30" t="n">
         <v>92.41</v>
@@ -1692,8 +1693,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>0.4876762828092646</v>
+      <c r="E31" s="1" t="n">
+        <v>0.49</v>
       </c>
       <c r="F31" t="n">
         <v>88.45</v>
@@ -1733,8 +1734,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>0.4823263700178126</v>
+      <c r="E32" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F32" t="n">
         <v>96.28</v>
@@ -1774,8 +1775,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>0.4816025608815385</v>
+      <c r="E33" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F33" t="n">
         <v>97.11</v>
@@ -1815,8 +1816,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>0.4811719604287907</v>
+      <c r="E34" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F34" t="n">
         <v>89.40000000000001</v>
@@ -1856,8 +1857,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>0.4780672713580246</v>
+      <c r="E35" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F35" t="n">
         <v>91.90000000000001</v>
@@ -1897,8 +1898,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>0.4776256351355191</v>
+      <c r="E36" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F36" t="n">
         <v>100</v>
@@ -1938,8 +1939,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>0.4768787316305536</v>
+      <c r="E37" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F37" t="n">
         <v>92.78</v>
@@ -1979,8 +1980,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>0.4750240494496366</v>
+      <c r="E38" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F38" t="n">
         <v>94.42</v>
@@ -2020,8 +2021,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>0.4744316225057632</v>
+      <c r="E39" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F39" t="n">
         <v>92.23</v>
@@ -2061,8 +2062,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>0.4732778096094423</v>
+      <c r="E40" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F40" t="n">
         <v>93.34</v>
@@ -2102,8 +2103,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>0.4704926443421159</v>
+      <c r="E41" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F41" t="n">
         <v>80.53</v>
@@ -2143,8 +2144,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>0.4692542180207449</v>
+      <c r="E42" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F42" t="n">
         <v>87.75</v>
@@ -2184,8 +2185,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>0.4679933451099388</v>
+      <c r="E43" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F43" t="n">
         <v>92.59</v>
@@ -2225,8 +2226,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v>0.4679844097301317</v>
+      <c r="E44" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F44" t="n">
         <v>96.44</v>
@@ -2266,8 +2267,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>0.4678991630603713</v>
+      <c r="E45" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F45" t="n">
         <v>88.06999999999999</v>
@@ -2307,8 +2308,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>0.4630571034763259</v>
+      <c r="E46" s="1" t="n">
+        <v>0.46</v>
       </c>
       <c r="F46" t="n">
         <v>98.91</v>
@@ -2348,8 +2349,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>0.4586367685855982</v>
+      <c r="E47" s="1" t="n">
+        <v>0.46</v>
       </c>
       <c r="F47" t="n">
         <v>91.16</v>
@@ -2389,8 +2390,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>0.4496681051973613</v>
+      <c r="E48" s="1" t="n">
+        <v>0.45</v>
       </c>
       <c r="F48" t="n">
         <v>96.09999999999999</v>
@@ -2430,8 +2431,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>0.4494362706740235</v>
+      <c r="E49" s="1" t="n">
+        <v>0.45</v>
       </c>
       <c r="F49" t="n">
         <v>90.93000000000001</v>
@@ -2471,8 +2472,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>0.446299503192475</v>
+      <c r="E50" s="1" t="n">
+        <v>0.45</v>
       </c>
       <c r="F50" t="n">
         <v>83.97</v>
@@ -2512,8 +2513,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>0.4451233570692567</v>
+      <c r="E51" s="1" t="n">
+        <v>0.45</v>
       </c>
       <c r="F51" t="n">
         <v>99.05</v>
@@ -2553,8 +2554,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>0.4418598067359545</v>
+      <c r="E52" s="1" t="n">
+        <v>0.44</v>
       </c>
       <c r="F52" t="n">
         <v>85.14</v>
@@ -2594,8 +2595,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v>0.4395880313520413</v>
+      <c r="E53" s="1" t="n">
+        <v>0.44</v>
       </c>
       <c r="F53" t="n">
         <v>82.70999999999999</v>
@@ -2635,8 +2636,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E54" t="n">
-        <v>0.4206696316873202</v>
+      <c r="E54" s="1" t="n">
+        <v>0.42</v>
       </c>
       <c r="F54" t="n">
         <v>84.58</v>
@@ -2676,8 +2677,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E55" t="n">
-        <v>0.420629244860268</v>
+      <c r="E55" s="1" t="n">
+        <v>0.42</v>
       </c>
       <c r="F55" t="n">
         <v>83.59999999999999</v>
@@ -2717,8 +2718,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E56" t="n">
-        <v>0.4134502935390508</v>
+      <c r="E56" s="1" t="n">
+        <v>0.41</v>
       </c>
       <c r="F56" t="n">
         <v>82.43000000000001</v>
@@ -2758,8 +2759,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E57" t="n">
-        <v>0.4097941594666012</v>
+      <c r="E57" s="1" t="n">
+        <v>0.41</v>
       </c>
       <c r="F57" t="n">
         <v>52.98</v>
@@ -2799,8 +2800,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E58" t="n">
-        <v>0.4009111521091335</v>
+      <c r="E58" s="1" t="n">
+        <v>0.4</v>
       </c>
       <c r="F58" t="n">
         <v>84.91</v>
@@ -2840,8 +2841,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E59" t="n">
-        <v>0.3899070793566656</v>
+      <c r="E59" s="1" t="n">
+        <v>0.39</v>
       </c>
       <c r="F59" t="n">
         <v>76.92</v>
@@ -2881,8 +2882,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>0.3883639908353363</v>
+      <c r="E60" s="1" t="n">
+        <v>0.39</v>
       </c>
       <c r="F60" t="n">
         <v>77.63</v>
@@ -2922,8 +2923,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E61" t="n">
-        <v>0.3832448575407101</v>
+      <c r="E61" s="1" t="n">
+        <v>0.38</v>
       </c>
       <c r="F61" t="n">
         <v>74.59</v>
@@ -2963,8 +2964,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E62" t="n">
-        <v>0.3831762242734187</v>
+      <c r="E62" s="1" t="n">
+        <v>0.38</v>
       </c>
       <c r="F62" t="n">
         <v>84.40000000000001</v>
@@ -3004,8 +3005,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E63" t="n">
-        <v>0.3620214003790248</v>
+      <c r="E63" s="1" t="n">
+        <v>0.36</v>
       </c>
       <c r="F63" t="n">
         <v>92.84999999999999</v>
@@ -3045,8 +3046,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E64" t="n">
-        <v>0.3391537550334465</v>
+      <c r="E64" s="1" t="n">
+        <v>0.34</v>
       </c>
       <c r="F64" t="n">
         <v>74.13</v>
@@ -3086,8 +3087,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E65" t="n">
-        <v>0.3375262327432809</v>
+      <c r="E65" s="1" t="n">
+        <v>0.34</v>
       </c>
       <c r="F65" t="n">
         <v>69.39</v>
@@ -3127,8 +3128,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v>0.3217485314950557</v>
+      <c r="E66" s="1" t="n">
+        <v>0.32</v>
       </c>
       <c r="F66" t="n">
         <v>61.9</v>
@@ -3168,8 +3169,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E67" t="n">
-        <v>0.2930568715896419</v>
+      <c r="E67" s="1" t="n">
+        <v>0.29</v>
       </c>
       <c r="F67" t="n">
         <v>58.24</v>
@@ -3209,8 +3210,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E68" t="n">
-        <v>0.2880491516203196</v>
+      <c r="E68" s="1" t="n">
+        <v>0.29</v>
       </c>
       <c r="F68" t="n">
         <v>58.78</v>
@@ -3250,8 +3251,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E69" t="n">
-        <v>0.2766337464115645</v>
+      <c r="E69" s="1" t="n">
+        <v>0.28</v>
       </c>
       <c r="F69" t="n">
         <v>56.62</v>
@@ -3291,8 +3292,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E70" t="n">
-        <v>0.2759208578629322</v>
+      <c r="E70" s="1" t="n">
+        <v>0.28</v>
       </c>
       <c r="F70" t="n">
         <v>63.8</v>
@@ -3332,8 +3333,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E71" t="n">
-        <v>0.2753370885178169</v>
+      <c r="E71" s="1" t="n">
+        <v>0.28</v>
       </c>
       <c r="F71" t="n">
         <v>56</v>
@@ -3373,8 +3374,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E72" t="n">
-        <v>0.2596426385914937</v>
+      <c r="E72" s="1" t="n">
+        <v>0.26</v>
       </c>
       <c r="F72" t="n">
         <v>96.86</v>
@@ -3414,8 +3415,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E73" t="n">
-        <v>0.2544084320848108</v>
+      <c r="E73" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F73" t="n">
         <v>47.24</v>
@@ -3455,8 +3456,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E74" t="n">
-        <v>0.2519548465686475</v>
+      <c r="E74" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F74" t="n">
         <v>24.77</v>
@@ -3496,8 +3497,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v>0.2509075926898587</v>
+      <c r="E75" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F75" t="n">
         <v>63.41</v>
@@ -3537,8 +3538,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E76" t="n">
-        <v>0.2503795395192028</v>
+      <c r="E76" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F76" t="n">
         <v>53.85</v>
@@ -3578,8 +3579,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E77" t="n">
-        <v>0.1933944351525965</v>
+      <c r="E77" s="1" t="n">
+        <v>0.19</v>
       </c>
       <c r="F77" t="n">
         <v>44.48</v>
@@ -3690,8 +3691,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.5457524239468542</v>
+      <c r="E2" s="1" t="n">
+        <v>0.55</v>
       </c>
       <c r="F2" t="n">
         <v>97.47</v>
@@ -3731,8 +3732,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.5192770534226446</v>
+      <c r="E3" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F3" t="n">
         <v>96.84999999999999</v>
@@ -3772,8 +3773,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.5022116034521068</v>
+      <c r="E4" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
         <v>100</v>
@@ -3813,8 +3814,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.4993247936699369</v>
+      <c r="E5" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F5" t="n">
         <v>96.90000000000001</v>
@@ -3854,8 +3855,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0.4919872546028742</v>
+      <c r="E6" s="1" t="n">
+        <v>0.49</v>
       </c>
       <c r="F6" t="n">
         <v>89.52</v>
@@ -3895,8 +3896,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.4902010290034317</v>
+      <c r="E7" s="1" t="n">
+        <v>0.49</v>
       </c>
       <c r="F7" t="n">
         <v>93.34999999999999</v>
@@ -3936,8 +3937,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.4894050312429654</v>
+      <c r="E8" s="1" t="n">
+        <v>0.49</v>
       </c>
       <c r="F8" t="n">
         <v>92.41</v>
@@ -3977,8 +3978,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0.4768787316305536</v>
+      <c r="E9" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F9" t="n">
         <v>92.78</v>
@@ -4018,8 +4019,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0.4494362706740235</v>
+      <c r="E10" s="1" t="n">
+        <v>0.45</v>
       </c>
       <c r="F10" t="n">
         <v>90.93000000000001</v>
@@ -4059,8 +4060,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0.4009111521091335</v>
+      <c r="E11" s="1" t="n">
+        <v>0.4</v>
       </c>
       <c r="F11" t="n">
         <v>84.91</v>
@@ -4100,8 +4101,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>0.3899070793566656</v>
+      <c r="E12" s="1" t="n">
+        <v>0.39</v>
       </c>
       <c r="F12" t="n">
         <v>76.92</v>
@@ -4141,8 +4142,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>0.3620214003790248</v>
+      <c r="E13" s="1" t="n">
+        <v>0.36</v>
       </c>
       <c r="F13" t="n">
         <v>92.84999999999999</v>
@@ -4253,8 +4254,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.5680751715371495</v>
+      <c r="E2" s="1" t="n">
+        <v>0.57</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -4294,8 +4295,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.5155802240655301</v>
+      <c r="E3" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -4335,8 +4336,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.5141586697424484</v>
+      <c r="E4" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F4" t="n">
         <v>98.56999999999999</v>
@@ -4376,8 +4377,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.5127737056159185</v>
+      <c r="E5" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -4417,8 +4418,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0.5125610382792181</v>
+      <c r="E6" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F6" t="n">
         <v>100</v>
@@ -4458,8 +4459,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.5095624877102957</v>
+      <c r="E7" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F7" t="n">
         <v>99.8</v>
@@ -4499,8 +4500,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.5042192403128086</v>
+      <c r="E8" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
         <v>99.06999999999999</v>
@@ -4540,8 +4541,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0.4876762828092646</v>
+      <c r="E9" s="1" t="n">
+        <v>0.49</v>
       </c>
       <c r="F9" t="n">
         <v>88.45</v>
@@ -4581,8 +4582,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0.4780672713580246</v>
+      <c r="E10" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F10" t="n">
         <v>91.90000000000001</v>
@@ -4622,8 +4623,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0.4776256351355191</v>
+      <c r="E11" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F11" t="n">
         <v>100</v>
@@ -4663,8 +4664,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>0.4750240494496366</v>
+      <c r="E12" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F12" t="n">
         <v>94.42</v>
@@ -4704,8 +4705,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>0.4744316225057632</v>
+      <c r="E13" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F13" t="n">
         <v>92.23</v>
@@ -4745,8 +4746,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>0.4732778096094423</v>
+      <c r="E14" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F14" t="n">
         <v>93.34</v>
@@ -4786,8 +4787,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>0.4692542180207449</v>
+      <c r="E15" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F15" t="n">
         <v>87.75</v>
@@ -4827,8 +4828,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0.4679933451099388</v>
+      <c r="E16" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F16" t="n">
         <v>92.59</v>
@@ -4868,8 +4869,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>0.4678991630603713</v>
+      <c r="E17" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F17" t="n">
         <v>88.06999999999999</v>
@@ -4909,8 +4910,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>0.4496681051973613</v>
+      <c r="E18" s="1" t="n">
+        <v>0.45</v>
       </c>
       <c r="F18" t="n">
         <v>96.09999999999999</v>
@@ -4950,8 +4951,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>0.446299503192475</v>
+      <c r="E19" s="1" t="n">
+        <v>0.45</v>
       </c>
       <c r="F19" t="n">
         <v>83.97</v>
@@ -4991,8 +4992,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>0.4451233570692567</v>
+      <c r="E20" s="1" t="n">
+        <v>0.45</v>
       </c>
       <c r="F20" t="n">
         <v>99.05</v>
@@ -5032,8 +5033,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>0.4418598067359545</v>
+      <c r="E21" s="1" t="n">
+        <v>0.44</v>
       </c>
       <c r="F21" t="n">
         <v>85.14</v>
@@ -5073,8 +5074,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>0.4395880313520413</v>
+      <c r="E22" s="1" t="n">
+        <v>0.44</v>
       </c>
       <c r="F22" t="n">
         <v>82.70999999999999</v>
@@ -5114,8 +5115,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>0.4206696316873202</v>
+      <c r="E23" s="1" t="n">
+        <v>0.42</v>
       </c>
       <c r="F23" t="n">
         <v>84.58</v>
@@ -5155,8 +5156,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>0.420629244860268</v>
+      <c r="E24" s="1" t="n">
+        <v>0.42</v>
       </c>
       <c r="F24" t="n">
         <v>83.59999999999999</v>
@@ -5196,8 +5197,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>0.4134502935390508</v>
+      <c r="E25" s="1" t="n">
+        <v>0.41</v>
       </c>
       <c r="F25" t="n">
         <v>82.43000000000001</v>
@@ -5237,8 +5238,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>0.4097941594666012</v>
+      <c r="E26" s="1" t="n">
+        <v>0.41</v>
       </c>
       <c r="F26" t="n">
         <v>52.98</v>
@@ -5278,8 +5279,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>0.3883639908353363</v>
+      <c r="E27" s="1" t="n">
+        <v>0.39</v>
       </c>
       <c r="F27" t="n">
         <v>77.63</v>
@@ -5319,8 +5320,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>0.3832448575407101</v>
+      <c r="E28" s="1" t="n">
+        <v>0.38</v>
       </c>
       <c r="F28" t="n">
         <v>74.59</v>
@@ -5360,8 +5361,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>0.3391537550334465</v>
+      <c r="E29" s="1" t="n">
+        <v>0.34</v>
       </c>
       <c r="F29" t="n">
         <v>74.13</v>
@@ -5401,8 +5402,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>0.3375262327432809</v>
+      <c r="E30" s="1" t="n">
+        <v>0.34</v>
       </c>
       <c r="F30" t="n">
         <v>69.39</v>
@@ -5442,8 +5443,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>0.3217485314950557</v>
+      <c r="E31" s="1" t="n">
+        <v>0.32</v>
       </c>
       <c r="F31" t="n">
         <v>61.9</v>
@@ -5483,8 +5484,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>0.2930568715896419</v>
+      <c r="E32" s="1" t="n">
+        <v>0.29</v>
       </c>
       <c r="F32" t="n">
         <v>58.24</v>
@@ -5524,8 +5525,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>0.2880491516203196</v>
+      <c r="E33" s="1" t="n">
+        <v>0.29</v>
       </c>
       <c r="F33" t="n">
         <v>58.78</v>
@@ -5565,8 +5566,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>0.2766337464115645</v>
+      <c r="E34" s="1" t="n">
+        <v>0.28</v>
       </c>
       <c r="F34" t="n">
         <v>56.62</v>
@@ -5606,8 +5607,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>0.2759208578629322</v>
+      <c r="E35" s="1" t="n">
+        <v>0.28</v>
       </c>
       <c r="F35" t="n">
         <v>63.8</v>
@@ -5647,8 +5648,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>0.2753370885178169</v>
+      <c r="E36" s="1" t="n">
+        <v>0.28</v>
       </c>
       <c r="F36" t="n">
         <v>56</v>
@@ -5688,8 +5689,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>0.2519548465686475</v>
+      <c r="E37" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F37" t="n">
         <v>24.77</v>
@@ -5729,8 +5730,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>0.2509075926898587</v>
+      <c r="E38" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F38" t="n">
         <v>63.41</v>
@@ -5770,8 +5771,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>0.2503795395192028</v>
+      <c r="E39" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F39" t="n">
         <v>53.85</v>
@@ -5811,8 +5812,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>0.1933944351525965</v>
+      <c r="E40" s="1" t="n">
+        <v>0.19</v>
       </c>
       <c r="F40" t="n">
         <v>44.48</v>
@@ -6079,8 +6080,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.5680751715371495</v>
+      <c r="E2" s="1" t="n">
+        <v>0.57</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -6120,8 +6121,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.5654832830138814</v>
+      <c r="E3" s="1" t="n">
+        <v>0.57</v>
       </c>
       <c r="F3" t="n">
         <v>96.23999999999999</v>
@@ -6161,8 +6162,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.5457524239468542</v>
+      <c r="E4" s="1" t="n">
+        <v>0.55</v>
       </c>
       <c r="F4" t="n">
         <v>97.47</v>
@@ -6202,8 +6203,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.5347131860269471</v>
+      <c r="E5" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F5" t="n">
         <v>99.43000000000001</v>
@@ -6243,8 +6244,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0.5325648407132801</v>
+      <c r="E6" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F6" t="n">
         <v>92.23</v>
@@ -6284,8 +6285,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.5300423012009458</v>
+      <c r="E7" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F7" t="n">
         <v>100</v>
@@ -6325,8 +6326,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.5260104700145199</v>
+      <c r="E8" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F8" t="n">
         <v>99</v>
@@ -6366,8 +6367,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0.5219467392588566</v>
+      <c r="E9" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F9" t="n">
         <v>99.83</v>
@@ -6407,8 +6408,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0.5192770534226446</v>
+      <c r="E10" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F10" t="n">
         <v>96.84999999999999</v>
@@ -6448,8 +6449,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0.5172977231558979</v>
+      <c r="E11" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F11" t="n">
         <v>98.33</v>
@@ -6560,8 +6561,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.1933944351525965</v>
+      <c r="E2" s="1" t="n">
+        <v>0.19</v>
       </c>
       <c r="F2" t="n">
         <v>44.48</v>
@@ -6584,11 +6585,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Itapeva</t>
+          <t>Pedra Bela</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6601,81 +6602,81 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.2503795395192028</v>
+      <c r="E3" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F3" t="n">
-        <v>53.85</v>
+        <v>24.77</v>
       </c>
       <c r="G3" t="n">
-        <v>13.77</v>
+        <v>13.52</v>
       </c>
       <c r="H3" t="n">
-        <v>28.17</v>
+        <v>3.28</v>
       </c>
       <c r="I3" t="n">
-        <v>279.82</v>
+        <v>6.98</v>
       </c>
       <c r="J3" t="n">
-        <v>35.67</v>
+        <v>21.45</v>
       </c>
       <c r="K3" t="n">
-        <v>59.98</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jarinú</t>
+          <t>Tuiuti</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sociedade de economia mista</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.2509075926898587</v>
+          <t>Empresa privada</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>63.41</v>
+        <v>47.24</v>
       </c>
       <c r="G4" t="n">
-        <v>16.27</v>
+        <v>23.95</v>
       </c>
       <c r="H4" t="n">
-        <v>29.56</v>
+        <v>50.99</v>
       </c>
       <c r="I4" t="n">
-        <v>7.58</v>
+        <v>25.82</v>
       </c>
       <c r="J4" t="n">
-        <v>31.03</v>
+        <v>39.51</v>
       </c>
       <c r="K4" t="n">
-        <v>52.25</v>
+        <v>52.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pedra Bela</t>
+          <t>Jarinú</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6683,35 +6684,35 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.2519548465686475</v>
+      <c r="E5" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F5" t="n">
-        <v>24.77</v>
+        <v>63.41</v>
       </c>
       <c r="G5" t="n">
-        <v>13.52</v>
+        <v>16.27</v>
       </c>
       <c r="H5" t="n">
-        <v>3.28</v>
+        <v>29.56</v>
       </c>
       <c r="I5" t="n">
-        <v>6.98</v>
+        <v>7.58</v>
       </c>
       <c r="J5" t="n">
-        <v>21.45</v>
+        <v>31.03</v>
       </c>
       <c r="K5" t="n">
-        <v>62.17</v>
+        <v>52.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tuiuti</t>
+          <t>Itapeva</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6721,29 +6722,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Empresa privada</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.2544084320848108</v>
+          <t>Sociedade de economia mista</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F6" t="n">
-        <v>47.24</v>
+        <v>53.85</v>
       </c>
       <c r="G6" t="n">
-        <v>23.95</v>
+        <v>13.77</v>
       </c>
       <c r="H6" t="n">
-        <v>50.99</v>
+        <v>28.17</v>
       </c>
       <c r="I6" t="n">
-        <v>25.82</v>
+        <v>279.82</v>
       </c>
       <c r="J6" t="n">
-        <v>39.51</v>
+        <v>35.67</v>
       </c>
       <c r="K6" t="n">
-        <v>52.26</v>
+        <v>59.98</v>
       </c>
     </row>
     <row r="7">
@@ -6765,8 +6766,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.2596426385914937</v>
+      <c r="E7" s="1" t="n">
+        <v>0.26</v>
       </c>
       <c r="F7" t="n">
         <v>96.86</v>
@@ -6789,16 +6790,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vargem</t>
+          <t>Mairiporã</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6806,40 +6807,40 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.2753370885178169</v>
+      <c r="E8" s="1" t="n">
+        <v>0.28</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>63.8</v>
       </c>
       <c r="G8" t="n">
-        <v>15.18</v>
+        <v>17.47</v>
       </c>
       <c r="H8" t="n">
-        <v>27.59</v>
+        <v>25.27</v>
       </c>
       <c r="I8" t="n">
-        <v>9.109999999999999</v>
+        <v>11.25</v>
       </c>
       <c r="J8" t="n">
-        <v>45.59</v>
+        <v>40.12</v>
       </c>
       <c r="K8" t="n">
-        <v>52.06</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mairiporã</t>
+          <t>Vargem</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6847,26 +6848,26 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0.2759208578629322</v>
+      <c r="E9" s="1" t="n">
+        <v>0.28</v>
       </c>
       <c r="F9" t="n">
-        <v>63.8</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>17.47</v>
+        <v>15.18</v>
       </c>
       <c r="H9" t="n">
-        <v>25.27</v>
+        <v>27.59</v>
       </c>
       <c r="I9" t="n">
-        <v>11.25</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>40.12</v>
+        <v>45.59</v>
       </c>
       <c r="K9" t="n">
-        <v>49.51</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="10">
@@ -6888,8 +6889,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0.2766337464115645</v>
+      <c r="E10" s="1" t="n">
+        <v>0.28</v>
       </c>
       <c r="F10" t="n">
         <v>56.62</v>
@@ -6929,8 +6930,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0.2880491516203196</v>
+      <c r="E11" s="1" t="n">
+        <v>0.29</v>
       </c>
       <c r="F11" t="n">
         <v>58.78</v>
@@ -7041,8 +7042,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.5680751715371495</v>
+      <c r="E2" s="1" t="n">
+        <v>0.57</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
@@ -7082,8 +7083,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.5192770534226446</v>
+      <c r="E3" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F3" t="n">
         <v>96.84999999999999</v>
@@ -7123,8 +7124,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.5165540506893349</v>
+      <c r="E4" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F4" t="n">
         <v>94.06999999999999</v>
@@ -7164,8 +7165,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.4919872546028742</v>
+      <c r="E5" s="1" t="n">
+        <v>0.49</v>
       </c>
       <c r="F5" t="n">
         <v>89.52</v>
@@ -7205,8 +7206,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0.4876762828092646</v>
+      <c r="E6" s="1" t="n">
+        <v>0.49</v>
       </c>
       <c r="F6" t="n">
         <v>88.45</v>
@@ -7246,8 +7247,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.4780672713580246</v>
+      <c r="E7" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F7" t="n">
         <v>91.90000000000001</v>
@@ -7287,8 +7288,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.4768787316305536</v>
+      <c r="E8" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F8" t="n">
         <v>92.78</v>
@@ -7328,8 +7329,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0.4744316225057632</v>
+      <c r="E9" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F9" t="n">
         <v>92.23</v>
@@ -7369,8 +7370,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0.4732778096094423</v>
+      <c r="E10" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F10" t="n">
         <v>93.34</v>
@@ -7410,8 +7411,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0.4704926443421159</v>
+      <c r="E11" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F11" t="n">
         <v>80.53</v>
@@ -7451,8 +7452,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>0.4692542180207449</v>
+      <c r="E12" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F12" t="n">
         <v>87.75</v>
@@ -7492,8 +7493,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>0.4678991630603713</v>
+      <c r="E13" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F13" t="n">
         <v>88.06999999999999</v>
@@ -7533,8 +7534,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>0.446299503192475</v>
+      <c r="E14" s="1" t="n">
+        <v>0.45</v>
       </c>
       <c r="F14" t="n">
         <v>83.97</v>
@@ -7574,8 +7575,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>0.4451233570692567</v>
+      <c r="E15" s="1" t="n">
+        <v>0.45</v>
       </c>
       <c r="F15" t="n">
         <v>99.05</v>
@@ -7615,8 +7616,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0.4418598067359545</v>
+      <c r="E16" s="1" t="n">
+        <v>0.44</v>
       </c>
       <c r="F16" t="n">
         <v>85.14</v>
@@ -7656,8 +7657,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>0.4097941594666012</v>
+      <c r="E17" s="1" t="n">
+        <v>0.41</v>
       </c>
       <c r="F17" t="n">
         <v>52.98</v>
@@ -7697,8 +7698,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>0.4009111521091335</v>
+      <c r="E18" s="1" t="n">
+        <v>0.4</v>
       </c>
       <c r="F18" t="n">
         <v>84.91</v>
@@ -7738,8 +7739,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>0.3899070793566656</v>
+      <c r="E19" s="1" t="n">
+        <v>0.39</v>
       </c>
       <c r="F19" t="n">
         <v>76.92</v>
@@ -7779,8 +7780,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>0.3832448575407101</v>
+      <c r="E20" s="1" t="n">
+        <v>0.38</v>
       </c>
       <c r="F20" t="n">
         <v>74.59</v>
@@ -7820,8 +7821,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>0.3620214003790248</v>
+      <c r="E21" s="1" t="n">
+        <v>0.36</v>
       </c>
       <c r="F21" t="n">
         <v>92.84999999999999</v>
@@ -7861,8 +7862,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>0.3375262327432809</v>
+      <c r="E22" s="1" t="n">
+        <v>0.34</v>
       </c>
       <c r="F22" t="n">
         <v>69.39</v>
@@ -7902,8 +7903,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>0.2880491516203196</v>
+      <c r="E23" s="1" t="n">
+        <v>0.29</v>
       </c>
       <c r="F23" t="n">
         <v>58.78</v>
@@ -7943,8 +7944,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>0.2753370885178169</v>
+      <c r="E24" s="1" t="n">
+        <v>0.28</v>
       </c>
       <c r="F24" t="n">
         <v>56</v>
@@ -7984,8 +7985,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>0.2544084320848108</v>
+      <c r="E25" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F25" t="n">
         <v>47.24</v>
@@ -8025,8 +8026,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>0.2519548465686475</v>
+      <c r="E26" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F26" t="n">
         <v>24.77</v>
@@ -8066,8 +8067,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>0.2503795395192028</v>
+      <c r="E27" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F27" t="n">
         <v>53.85</v>
@@ -8107,8 +8108,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>0.1933944351525965</v>
+      <c r="E28" s="1" t="n">
+        <v>0.19</v>
       </c>
       <c r="F28" t="n">
         <v>44.48</v>
@@ -8219,8 +8220,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.5654832830138814</v>
+      <c r="E2" s="1" t="n">
+        <v>0.57</v>
       </c>
       <c r="F2" t="n">
         <v>96.23999999999999</v>
@@ -8260,8 +8261,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.5300423012009458</v>
+      <c r="E3" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -8301,8 +8302,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.5260104700145199</v>
+      <c r="E4" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F4" t="n">
         <v>99</v>
@@ -8342,8 +8343,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.5172977231558979</v>
+      <c r="E5" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F5" t="n">
         <v>98.33</v>
@@ -8383,8 +8384,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0.5022116034521068</v>
+      <c r="E6" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F6" t="n">
         <v>100</v>
@@ -8424,8 +8425,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.4968397909795718</v>
+      <c r="E7" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F7" t="n">
         <v>97.94</v>
@@ -8465,8 +8466,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.4964879726116124</v>
+      <c r="E8" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
         <v>92.12</v>
@@ -8506,8 +8507,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0.4902010290034317</v>
+      <c r="E9" s="1" t="n">
+        <v>0.49</v>
       </c>
       <c r="F9" t="n">
         <v>93.34999999999999</v>
@@ -8547,8 +8548,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0.4894050312429654</v>
+      <c r="E10" s="1" t="n">
+        <v>0.49</v>
       </c>
       <c r="F10" t="n">
         <v>92.41</v>
@@ -8588,8 +8589,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0.4630571034763259</v>
+      <c r="E11" s="1" t="n">
+        <v>0.46</v>
       </c>
       <c r="F11" t="n">
         <v>98.91</v>
@@ -8629,8 +8630,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>0.4395880313520413</v>
+      <c r="E12" s="1" t="n">
+        <v>0.44</v>
       </c>
       <c r="F12" t="n">
         <v>82.70999999999999</v>
@@ -8670,8 +8671,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>0.420629244860268</v>
+      <c r="E13" s="1" t="n">
+        <v>0.42</v>
       </c>
       <c r="F13" t="n">
         <v>83.59999999999999</v>
@@ -8711,8 +8712,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>0.3883639908353363</v>
+      <c r="E14" s="1" t="n">
+        <v>0.39</v>
       </c>
       <c r="F14" t="n">
         <v>77.63</v>
@@ -8752,8 +8753,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>0.3391537550334465</v>
+      <c r="E15" s="1" t="n">
+        <v>0.34</v>
       </c>
       <c r="F15" t="n">
         <v>74.13</v>
@@ -8793,8 +8794,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0.3217485314950557</v>
+      <c r="E16" s="1" t="n">
+        <v>0.32</v>
       </c>
       <c r="F16" t="n">
         <v>61.9</v>
@@ -8834,8 +8835,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>0.2766337464115645</v>
+      <c r="E17" s="1" t="n">
+        <v>0.28</v>
       </c>
       <c r="F17" t="n">
         <v>56.62</v>
@@ -8875,8 +8876,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>0.2509075926898587</v>
+      <c r="E18" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F18" t="n">
         <v>63.41</v>
@@ -8987,8 +8988,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.5457524239468542</v>
+      <c r="E2" s="1" t="n">
+        <v>0.55</v>
       </c>
       <c r="F2" t="n">
         <v>97.47</v>
@@ -9028,8 +9029,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.5127737056159185</v>
+      <c r="E3" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -9069,8 +9070,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.5081899659912953</v>
+      <c r="E4" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F4" t="n">
         <v>96.25</v>
@@ -9110,8 +9111,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.4993247936699369</v>
+      <c r="E5" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F5" t="n">
         <v>96.90000000000001</v>
@@ -9151,8 +9152,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0.4816025608815385</v>
+      <c r="E6" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F6" t="n">
         <v>97.11</v>
@@ -9192,8 +9193,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.4811719604287907</v>
+      <c r="E7" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F7" t="n">
         <v>89.40000000000001</v>
@@ -9233,8 +9234,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.4776256351355191</v>
+      <c r="E8" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F8" t="n">
         <v>100</v>
@@ -9274,8 +9275,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0.4586367685855982</v>
+      <c r="E9" s="1" t="n">
+        <v>0.46</v>
       </c>
       <c r="F9" t="n">
         <v>91.16</v>
@@ -9315,8 +9316,8 @@
           <t>Município</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0.4494362706740235</v>
+      <c r="E10" s="1" t="n">
+        <v>0.45</v>
       </c>
       <c r="F10" t="n">
         <v>90.93000000000001</v>
@@ -9356,8 +9357,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0.4206696316873202</v>
+      <c r="E11" s="1" t="n">
+        <v>0.42</v>
       </c>
       <c r="F11" t="n">
         <v>84.58</v>
@@ -9397,8 +9398,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>0.4134502935390508</v>
+      <c r="E12" s="1" t="n">
+        <v>0.41</v>
       </c>
       <c r="F12" t="n">
         <v>82.43000000000001</v>
@@ -9438,8 +9439,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>0.2930568715896419</v>
+      <c r="E13" s="1" t="n">
+        <v>0.29</v>
       </c>
       <c r="F13" t="n">
         <v>58.24</v>
@@ -9479,8 +9480,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>0.2759208578629322</v>
+      <c r="E14" s="1" t="n">
+        <v>0.28</v>
       </c>
       <c r="F14" t="n">
         <v>63.8</v>
@@ -9591,8 +9592,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.5347131860269471</v>
+      <c r="E2" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F2" t="n">
         <v>99.43000000000001</v>
@@ -9632,8 +9633,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.5325648407132801</v>
+      <c r="E3" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F3" t="n">
         <v>92.23</v>
@@ -9673,8 +9674,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.5219467392588566</v>
+      <c r="E4" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F4" t="n">
         <v>99.83</v>
@@ -9714,8 +9715,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.5155802240655301</v>
+      <c r="E5" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -9755,8 +9756,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0.5141586697424484</v>
+      <c r="E6" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F6" t="n">
         <v>98.56999999999999</v>
@@ -9796,8 +9797,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.5139840024875143</v>
+      <c r="E7" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F7" t="n">
         <v>99.56</v>
@@ -9837,8 +9838,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.5125610382792181</v>
+      <c r="E8" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F8" t="n">
         <v>100</v>
@@ -9878,8 +9879,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0.5095624877102957</v>
+      <c r="E9" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F9" t="n">
         <v>99.8</v>
@@ -9919,8 +9920,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0.5072676042789033</v>
+      <c r="E10" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F10" t="n">
         <v>95.09</v>
@@ -9960,8 +9961,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0.5056631921207716</v>
+      <c r="E11" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F11" t="n">
         <v>96.98</v>
@@ -10001,8 +10002,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>0.5042192403128086</v>
+      <c r="E12" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F12" t="n">
         <v>99.06999999999999</v>
@@ -10042,8 +10043,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>0.4958342209485269</v>
+      <c r="E13" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F13" t="n">
         <v>89.78</v>
@@ -10083,8 +10084,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>0.4823263700178126</v>
+      <c r="E14" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F14" t="n">
         <v>96.28</v>
@@ -10124,8 +10125,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>0.4750240494496366</v>
+      <c r="E15" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F15" t="n">
         <v>94.42</v>
@@ -10165,8 +10166,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0.4679933451099388</v>
+      <c r="E16" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F16" t="n">
         <v>92.59</v>
@@ -10206,8 +10207,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>0.4679844097301317</v>
+      <c r="E17" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F17" t="n">
         <v>96.44</v>
@@ -10247,8 +10248,8 @@
           <t>Sociedade de economia mista</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>0.4496681051973613</v>
+      <c r="E18" s="1" t="n">
+        <v>0.45</v>
       </c>
       <c r="F18" t="n">
         <v>96.09999999999999</v>
@@ -10288,8 +10289,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>0.3831762242734187</v>
+      <c r="E19" s="1" t="n">
+        <v>0.38</v>
       </c>
       <c r="F19" t="n">
         <v>84.40000000000001</v>
@@ -10329,8 +10330,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>0.2596426385914937</v>
+      <c r="E20" s="1" t="n">
+        <v>0.26</v>
       </c>
       <c r="F20" t="n">
         <v>96.86</v>
@@ -10441,8 +10442,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.5654832830138814</v>
+      <c r="E2" s="1" t="n">
+        <v>0.57</v>
       </c>
       <c r="F2" t="n">
         <v>96.23999999999999</v>
@@ -10482,8 +10483,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.5347131860269471</v>
+      <c r="E3" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F3" t="n">
         <v>99.43000000000001</v>
@@ -10523,8 +10524,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.5325648407132801</v>
+      <c r="E4" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F4" t="n">
         <v>92.23</v>
@@ -10564,8 +10565,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.5300423012009458</v>
+      <c r="E5" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F5" t="n">
         <v>100</v>
@@ -10605,8 +10606,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0.5260104700145199</v>
+      <c r="E6" s="1" t="n">
+        <v>0.53</v>
       </c>
       <c r="F6" t="n">
         <v>99</v>
@@ -10646,8 +10647,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.5219467392588566</v>
+      <c r="E7" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F7" t="n">
         <v>99.83</v>
@@ -10687,8 +10688,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.5172977231558979</v>
+      <c r="E8" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F8" t="n">
         <v>98.33</v>
@@ -10728,8 +10729,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0.5165540506893349</v>
+      <c r="E9" s="1" t="n">
+        <v>0.52</v>
       </c>
       <c r="F9" t="n">
         <v>94.06999999999999</v>
@@ -10769,8 +10770,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0.5081899659912953</v>
+      <c r="E10" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F10" t="n">
         <v>96.25</v>
@@ -10810,8 +10811,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0.5072676042789033</v>
+      <c r="E11" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F11" t="n">
         <v>95.09</v>
@@ -10851,8 +10852,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>0.4964879726116124</v>
+      <c r="E12" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F12" t="n">
         <v>92.12</v>
@@ -10892,8 +10893,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>0.4958342209485269</v>
+      <c r="E13" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F13" t="n">
         <v>89.78</v>
@@ -10933,8 +10934,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>0.4823263700178126</v>
+      <c r="E14" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F14" t="n">
         <v>96.28</v>
@@ -10974,8 +10975,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>0.4816025608815385</v>
+      <c r="E15" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F15" t="n">
         <v>97.11</v>
@@ -11015,8 +11016,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0.4811719604287907</v>
+      <c r="E16" s="1" t="n">
+        <v>0.48</v>
       </c>
       <c r="F16" t="n">
         <v>89.40000000000001</v>
@@ -11056,8 +11057,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>0.4630571034763259</v>
+      <c r="E17" s="1" t="n">
+        <v>0.46</v>
       </c>
       <c r="F17" t="n">
         <v>98.91</v>
@@ -11097,8 +11098,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>0.4586367685855982</v>
+      <c r="E18" s="1" t="n">
+        <v>0.46</v>
       </c>
       <c r="F18" t="n">
         <v>91.16</v>
@@ -11138,8 +11139,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>0.3831762242734187</v>
+      <c r="E19" s="1" t="n">
+        <v>0.38</v>
       </c>
       <c r="F19" t="n">
         <v>84.40000000000001</v>
@@ -11179,8 +11180,8 @@
           <t>Autarquia</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>0.2596426385914937</v>
+      <c r="E20" s="1" t="n">
+        <v>0.26</v>
       </c>
       <c r="F20" t="n">
         <v>96.86</v>
@@ -11291,8 +11292,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.5139840024875143</v>
+      <c r="E2" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F2" t="n">
         <v>99.56</v>
@@ -11332,8 +11333,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.5056631921207716</v>
+      <c r="E3" s="1" t="n">
+        <v>0.51</v>
       </c>
       <c r="F3" t="n">
         <v>96.98</v>
@@ -11373,8 +11374,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.4968397909795718</v>
+      <c r="E4" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
         <v>97.94</v>
@@ -11414,8 +11415,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.4704926443421159</v>
+      <c r="E5" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F5" t="n">
         <v>80.53</v>
@@ -11455,8 +11456,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0.4679844097301317</v>
+      <c r="E6" s="1" t="n">
+        <v>0.47</v>
       </c>
       <c r="F6" t="n">
         <v>96.44</v>
@@ -11496,8 +11497,8 @@
           <t>Empresa privada</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.2544084320848108</v>
+      <c r="E7" s="1" t="n">
+        <v>0.25</v>
       </c>
       <c r="F7" t="n">
         <v>47.24</v>
